--- a/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,10 +484,8 @@
           <t>2026-09-20 07:15:18</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B2" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -542,10 +540,8 @@
           <t>2026-09-20 07:15:18</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B3" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,6 +587,456 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>Untuk Keperluan sumur di cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:35</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>250</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:35</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:35</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:35</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:35</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>50</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:35</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>50</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:41:35</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>115</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:18:37</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -988,10 +988,8 @@
           <t>2026-09-21 13:18:37</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B11" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1037,6 +1035,586 @@
       <c r="L11" t="inlineStr">
         <is>
           <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Aqua 600 ml</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>240</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic di Lapangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>24</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic di Lapangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:08</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>24</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic di Lapangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:08</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>48</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic di Lapangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:08</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>48</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic di Lapangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Coca Cola</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>48</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic di Lapangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:08</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Fanta</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>48</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic di Lapangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:08</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>48</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic di Lapangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:08</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>48</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic di Lapangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:24:08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>48</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic di Lapangan</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1041,7 +1041,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:08</t>
+          <t>2026-10-03 06:57:42</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1099,7 +1099,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:08</t>
+          <t>2026-10-03 06:57:42</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:08</t>
+          <t>2026-10-03 06:57:42</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1215,7 +1215,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:08</t>
+          <t>2026-10-03 06:57:42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1273,7 +1273,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:08</t>
+          <t>2026-10-03 06:57:42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1331,7 +1331,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:08</t>
+          <t>2026-10-03 06:57:42</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Coca Cola</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1389,7 +1389,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:08</t>
+          <t>2026-10-03 06:57:42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fanta</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1447,7 +1447,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:08</t>
+          <t>2026-10-03 06:57:42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1505,7 +1505,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:08</t>
+          <t>2026-10-03 06:57:42</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1563,7 +1563,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-30 13:24:08</t>
+          <t>2026-10-03 06:57:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1609,10 +1609,126 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic di Lapangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:57:42</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>11</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>36</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic di Lapangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:57:42</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>12</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>72</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>Kebutuhan Logistic di Lapangan</t>
         </is>

--- a/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,10 +1044,8 @@
           <t>2026-10-03 06:57:42</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B12" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1102,10 +1100,8 @@
           <t>2026-10-03 06:57:42</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B13" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1160,10 +1156,8 @@
           <t>2026-10-03 06:57:42</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B14" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1218,10 +1212,8 @@
           <t>2026-10-03 06:57:42</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B15" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1276,10 +1268,8 @@
           <t>2026-10-03 06:57:42</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B16" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1334,10 +1324,8 @@
           <t>2026-10-03 06:57:42</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B17" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1392,10 +1380,8 @@
           <t>2026-10-03 06:57:42</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B18" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1450,10 +1436,8 @@
           <t>2026-10-03 06:57:42</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B19" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1508,10 +1492,8 @@
           <t>2026-10-03 06:57:42</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B20" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1566,10 +1548,8 @@
           <t>2026-10-03 06:57:42</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B21" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1624,10 +1604,8 @@
           <t>2026-10-03 06:57:42</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B22" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1682,10 +1660,8 @@
           <t>2026-10-03 06:57:42</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B23" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1731,6 +1707,702 @@
       <c r="L23" t="inlineStr">
         <is>
           <t>Kebutuhan Logistic di Lapangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:28</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Indocafe Coffemix Renteng</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:28</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:28</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Nescafe Classic renteng</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:28</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>72</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:28</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>72</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>7</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>72</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:28</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>72</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:28</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>9</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>48</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:28</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Coklat</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:28</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>11</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Keju</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>10</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:00:28</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>12</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -985,7 +985,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21 13:18:37</t>
+          <t>2026-10-03 06:57:42</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -993,7 +993,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1011,30 +1011,30 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>240</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Kebutuhan Logistic di Lapangan</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1184,11 +1184,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1576,11 +1576,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1632,11 +1632,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-03 12:00:28</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1688,25 +1688,25 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic di Lapangan</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
@@ -1716,10 +1716,8 @@
           <t>2026-10-03 12:00:28</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B24" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1737,7 +1735,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1746,11 +1744,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1774,10 +1772,8 @@
           <t>2026-10-03 12:00:28</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B25" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1795,7 +1791,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1804,11 +1800,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1832,10 +1828,8 @@
           <t>2026-10-03 12:00:28</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B26" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1853,7 +1847,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1862,11 +1856,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1890,10 +1884,8 @@
           <t>2026-10-03 12:00:28</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B27" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1911,7 +1903,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1920,11 +1912,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1948,10 +1940,8 @@
           <t>2026-10-03 12:00:28</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B28" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1969,7 +1959,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1978,11 +1968,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2006,10 +1996,8 @@
           <t>2026-10-03 12:00:28</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B29" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2027,7 +2015,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2036,7 +2024,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2064,10 +2052,8 @@
           <t>2026-10-03 12:00:28</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B30" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2085,7 +2071,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2094,7 +2080,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2122,10 +2108,8 @@
           <t>2026-10-03 12:00:28</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B31" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2143,7 +2127,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2152,11 +2136,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2180,10 +2164,8 @@
           <t>2026-10-03 12:00:28</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B32" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2201,7 +2183,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2210,11 +2192,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2238,10 +2220,8 @@
           <t>2026-10-03 12:00:28</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B33" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2259,7 +2239,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2268,7 +2248,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2296,10 +2276,8 @@
           <t>2026-10-03 12:00:28</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B34" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2317,7 +2295,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2326,7 +2304,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2351,58 +2329,1368 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+          <t>2026-10-05 09:23:59</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Indocafe Coffemix Renteng</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:59</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:59</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Nescafe Classic renteng</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:59</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>72</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:59</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>10</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:59</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>72</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:59</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>7</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>72</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:59</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>72</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:59</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>9</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>48</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:59</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Coklat</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:59</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>11</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Keju</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>10</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:23:59</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>12</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:52:53</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>7201250141</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Indocafe Coffemix Renteng</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:52:53</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>6</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:52:53</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Nescafe Classic renteng</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>5</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:52:53</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>72</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:52:53</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>10</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:52:53</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>6</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>72</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:52:53</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>7</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>72</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:52:53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>72</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:52:53</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>9</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>48</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:52:53</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>10</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Coklat</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>10</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:52:53</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>11</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Keju</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>10</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:52:53</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
         <v>12</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ESTIMATED SUM</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="I58" t="n">
         <v>10</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Ea</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3004,10 +3004,8 @@
           <t>2026-10-05 09:52:53</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B47" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3062,10 +3060,8 @@
           <t>2026-10-05 09:52:53</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B48" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3120,10 +3116,8 @@
           <t>2026-10-05 09:52:53</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B49" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3178,10 +3172,8 @@
           <t>2026-10-05 09:52:53</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B50" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -3236,10 +3228,8 @@
           <t>2026-10-05 09:52:53</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B51" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -3294,10 +3284,8 @@
           <t>2026-10-05 09:52:53</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B52" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -3352,10 +3340,8 @@
           <t>2026-10-05 09:52:53</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B53" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3410,10 +3396,8 @@
           <t>2026-10-05 09:52:53</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B54" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3468,10 +3452,8 @@
           <t>2026-10-05 09:52:53</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B55" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3526,10 +3508,8 @@
           <t>2026-10-05 09:52:53</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B56" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3584,10 +3564,8 @@
           <t>2026-10-05 09:52:53</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B57" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3642,10 +3620,8 @@
           <t>2026-10-05 09:52:53</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B58" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3691,6 +3667,122 @@
       <c r="L58" t="inlineStr">
         <is>
           <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:52:43</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>049/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Aqua 600 ml</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>2188</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:52:43</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>049/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Aqua Galon Segel</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>15</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3676,10 +3676,8 @@
           <t>2026-10-06 18:52:43</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B59" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3734,10 +3732,8 @@
           <t>2026-10-06 18:52:43</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B60" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3783,6 +3779,234 @@
       <c r="L60" t="inlineStr">
         <is>
           <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:24:24</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>50</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:24:24</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>50</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:54:06</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:54:06</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
+++ b/database_penyimpanan_aman/database_bastb_tersimpan.xlsx
@@ -985,7 +985,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-06 18:52:43</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -993,7 +993,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1016,11 +1016,11 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>240</v>
+        <v>2188</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1029,19 +1029,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic di Lapangan</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-06 18:52:43</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1072,11 +1072,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1085,19 +1085,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic di Lapangan</t>
+          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-14 13:24:24</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1115,45 +1115,45 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic di Lapangan</t>
+          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-14 13:24:24</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1171,45 +1171,45 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic di Lapangan</t>
+          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-14 13:54:06</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1227,24 +1227,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1253,19 +1253,19 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic di Lapangan</t>
+          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-14 13:54:06</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1283,24 +1283,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1309,19 +1309,19 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic di Lapangan</t>
+          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-16 10:49:23</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1352,15 +1352,15 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-16 10:49:23</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1408,15 +1408,15 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1433,7 +1433,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-16 10:49:23</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1464,15 +1464,15 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-16 10:49:23</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1545,7 +1545,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-16 10:49:23</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1576,20 +1576,20 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-03 06:57:42</t>
+          <t>2026-10-16 10:49:23</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1632,15 +1632,15 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
+          <t>2026-10-16 10:49:23</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1688,32 +1688,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Kebutuhan Logistic di Lapangan</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
+          <t>2026-10-16 10:49:23</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1731,11 +1731,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1744,32 +1744,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Kebutuhan Logistic di Lapangan</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
+          <t>2026-10-16 10:49:23</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1787,11 +1787,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Kebutuhan Logistic di Lapangan</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
+          <t>2026-10-16 10:49:23</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1843,11 +1843,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1856,32 +1856,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Kebutuhan Logistic di Lapangan</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
+          <t>2026-10-16 10:49:23</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1899,11 +1899,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1912,32 +1912,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Kebutuhan Logistic di Lapangan</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
+          <t>2026-10-16 10:49:23</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1955,11 +1955,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1976,24 +1976,24 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Kebutuhan Logistic di Lapangan</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
+          <t>2026-10-16 10:58:55</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2024,11 +2024,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
+          <t>2026-10-16 10:58:55</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2080,11 +2080,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
+          <t>2026-10-16 10:58:55</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2136,11 +2136,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
+          <t>2026-10-16 10:58:55</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2192,11 +2192,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
+          <t>2026-10-16 10:58:55</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2273,7 +2273,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:28</t>
+          <t>2026-10-16 10:58:55</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2304,11 +2304,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:59</t>
+          <t>2026-10-16 10:58:55</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2347,11 +2347,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2360,11 +2360,11 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2373,19 +2373,19 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:59</t>
+          <t>2026-10-16 10:58:55</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2403,11 +2403,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2416,11 +2416,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:59</t>
+          <t>2026-10-16 10:58:55</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2459,11 +2459,11 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2472,11 +2472,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2485,19 +2485,19 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:59</t>
+          <t>2026-10-16 10:58:55</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2515,11 +2515,11 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2528,11 +2528,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2541,19 +2541,19 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:59</t>
+          <t>2026-10-16 10:58:55</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2571,11 +2571,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2597,19 +2597,19 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:59</t>
+          <t>2026-10-16 10:58:55</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2627,11 +2627,11 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2640,11 +2640,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2653,19 +2653,19 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:59</t>
+          <t>2026-10-16 11:08:29</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2683,11 +2683,11 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2696,32 +2696,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:59</t>
+          <t>2026-10-16 11:08:29</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2739,11 +2739,11 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2752,11 +2752,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2765,19 +2765,19 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:59</t>
+          <t>2026-10-16 11:08:29</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2795,11 +2795,11 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2808,11 +2808,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2821,19 +2821,19 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:59</t>
+          <t>2026-10-16 11:08:29</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2851,11 +2851,11 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2864,11 +2864,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:59</t>
+          <t>2026-10-16 11:08:29</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2907,11 +2907,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -2933,19 +2933,19 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-05 09:23:59</t>
+          <t>2026-10-16 11:08:29</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2963,11 +2963,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2976,11 +2976,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2989,19 +2989,19 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:53</t>
+          <t>2026-10-16 11:08:29</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3032,15 +3032,15 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3050,14 +3050,14 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:53</t>
+          <t>2026-10-16 11:08:29</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3088,11 +3088,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:53</t>
+          <t>2026-10-16 11:08:29</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3144,11 +3144,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:53</t>
+          <t>2026-10-16 11:08:29</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3200,11 +3200,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:53</t>
+          <t>2026-10-16 11:08:29</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3281,7 +3281,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:53</t>
+          <t>2026-10-16 11:08:29</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3312,11 +3312,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3337,15 +3337,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:53</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>7201250141</v>
+          <t>2026-10-16 11:30:34</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3355,11 +3357,11 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3368,11 +3370,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3381,27 +3383,29 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:53</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>7201250141</v>
+          <t>2026-10-16 11:30:34</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3411,11 +3415,11 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3424,11 +3428,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3437,27 +3441,29 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:53</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>7201250141</v>
+          <t>2026-10-16 11:30:34</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3467,11 +3473,11 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3480,11 +3486,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3493,27 +3499,29 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:53</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>7201250141</v>
+          <t>2026-10-16 11:30:34</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3523,11 +3531,11 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3536,11 +3544,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3549,27 +3557,29 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:53</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>7201250141</v>
+          <t>2026-10-16 11:30:34</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3579,11 +3589,11 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3592,7 +3602,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3605,27 +3615,29 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:53</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>7201250141</v>
+          <t>2026-10-16 11:30:34</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3635,11 +3647,11 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3648,11 +3660,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3661,27 +3673,29 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-06 18:52:43</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>7201250141</v>
+          <t>2026-10-16 11:30:34</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3691,11 +3705,11 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3704,11 +3718,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2188</v>
+        <v>72</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3717,27 +3731,29 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-06 18:52:43</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>7201250141</v>
+          <t>2026-10-16 11:30:34</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3747,11 +3763,11 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3760,11 +3776,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3773,27 +3789,29 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-14 13:24:24</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>7201250141</v>
+          <t>2026-10-16 11:30:34</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3803,53 +3821,55 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-14 13:24:24</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>7201250141</v>
+          <t>2026-10-16 11:30:34</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3859,45 +3879,45 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-14 13:54:06</t>
+          <t>2026-10-16 11:30:34</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3907,7 +3927,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3917,24 +3937,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3943,19 +3963,19 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-14 13:54:06</t>
+          <t>2026-10-16 11:30:34</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3965,7 +3985,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3975,24 +3995,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4001,12 +4021,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
     </row>
